--- a/var/data/original_files/Articles A august 24.xlsx
+++ b/var/data/original_files/Articles A august 24.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,11 +488,6 @@
           <t>Full Link</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Coordinates</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,11 +539,6 @@
           <t>https://www.iaea.org/newscenter/pressreleases/iaea-reviews-progress-of-sri-lankas-nuclear-infrastructure-development</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>(6.9388614, 79.8542005)</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -600,11 +590,6 @@
           <t>https://www.iaea.org/publications/15871/global-status-of-front-end-nuclear-fuel-cycle-inventories-in-2023</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -656,11 +641,6 @@
           <t>https://www.aljazeera.com/news/2025/7/20/iran-to-hold-nuclear-talks-with-3-european-powers-on-friday</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>(41.335895, 34.0204704)</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -712,7 +692,6 @@
           <t>https://anewz.tv/world/world-news/11030/iran-russia-and-china-hold-nuclear-talks-in-tehran/news</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -764,7 +743,6 @@
           <t>https://www.france24.com/en/middle-east/20250722-iran-nuclear-enrichment-european-talks</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -816,11 +794,6 @@
           <t>https://trt.global/afrika-english/article/cb1ed0cb19e6</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>(32.0852997, 34.7818064)</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -872,11 +845,6 @@
           <t>https://mezha.net/eng/bukvy/kansai-electric-power-launches-new-nuclear-reactor-research-in-japan/</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>(35.9263502, 136.6068127)</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -928,11 +896,6 @@
           <t>https://www.energy.gov/em/articles/cleanup-crews-find-solution-improve-spent-nuclear-fuel-processing-srs</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>(18.3640277, -65.9526469)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -942,7 +905,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Chemical, Biological, Radiological, Nuclear, Explosive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -984,16 +947,11 @@
           <t>https://www.army.mil/article/287249</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1003,17 +961,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FBI and WMD Civil Support Team strengthen partnership during Fort Meade Exercise</t>
+          <t>New surveillance tool can predict COVID variants of concern</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
@@ -1027,7 +985,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1037,39 +995,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.army.mil/article/287249</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://www.cidrap.umn.edu/covid-19/new-surveillance-tool-can-predict-covid-variants-concern</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FBI and WMD Civil Support Team strengthen partnership during Fort Meade Exercise</t>
+          <t xml:space="preserve">China Avian Influenza Report </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1093,49 +1046,44 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.army.mil/article/287249</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://www.chp.gov.hk/files/pdf/2025_avian_influenza_report_vol21_wk29.pdf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FBI and WMD Civil Support Team strengthen partnership during Fort Meade Exercise</t>
+          <t>Cambodian boy in ICU with H5N1 avian flu infection</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1149,43 +1097,38 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.army.mil/article/287249</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://www.cidrap.umn.edu/avian-influenza-bird-flu/cambodian-boy-icu-h5n1-avian-flu-infection</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FBI and WMD Civil Support Team strengthen partnership during Fort Meade Exercise</t>
+          <t>India strengthens nuclear disaster preparedness: Home Ministry</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>New Delhi</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1205,12 +1148,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.army.mil/article/287249</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://www.greaterkashmir.com/national/india-strengthens-nuclear-disaster-preparedness-home-ministry/</t>
         </is>
       </c>
     </row>
@@ -1222,26 +1160,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New surveillance tool can predict COVID variants of concern</t>
+          <t>Egypt to launch 1st El-Dabaa Nuclear Reactor in H2 2028</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>El Dabaa</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1251,7 +1189,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1261,43 +1199,38 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/covid-19/new-surveillance-tool-can-predict-covid-variants-concern</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>(48.1371079, 11.5753822)</t>
+          <t>https://www.businesstodayegypt.com/Article/1/6553/Egypt-to-launch-1st-El-Dabaa-Nuclear-Reactor-in-H2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">China Avian Influenza Report </t>
+          <t>Iran agrees to visit by team from UN nuclear watchdog in coming weeks</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>45860</v>
+        <v>45861</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1307,7 +1240,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1317,12 +1250,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/files/pdf/2025_avian_influenza_report_vol21_wk29.pdf</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>(31.2098936, 121.313029)</t>
+          <t>https://www.reuters.com/world/middle-east/iran-agrees-visit-by-team-un-nuclear-watchdog-coming-weeks-2025-07-23/</t>
         </is>
       </c>
     </row>
@@ -1334,82 +1262,77 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cambodian boy in ICU with H5N1 avian flu infection</t>
+          <t>Blast in Syria’s Idlib kills at least six, injures over 100, state media say</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Idlib</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>45861</v>
+        <v>45862</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human, Infrastructure</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/avian-influenza-bird-flu/cambodian-boy-icu-h5n1-avian-flu-infection</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>(11.5730391, 104.857807)</t>
+          <t>https://english.alarabiya.net/amp/News/middle-east/2025/07/24/explosion-heard-in-idlib-syrian-media-report</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>India strengthens nuclear disaster preparedness: Home Ministry</t>
+          <t>Radiation-Resistant Bacterium Discovered in Irradiator Pool Challenges Safety Assumptions</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45861</v>
+        <v>45860</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1429,12 +1352,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/india-strengthens-nuclear-disaster-preparedness-home-ministry/</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>(28.5982897, 77.1234689)</t>
+          <t>https://globalbiodefense.com/2025/07/22/radiation-resistant-bacillus-cereus-irradiator-discovery/</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1364,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt to launch 1st El-Dabaa Nuclear Reactor in H2 2028</t>
+          <t>What the WHO Pandemic Agreement and IHR Reforms Mean for the Future of Pandemic Preparedness</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>El Dabaa</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -1475,7 +1393,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1485,12 +1403,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.businesstodayegypt.com/Article/1/6553/Egypt-to-launch-1st-El-Dabaa-Nuclear-Reactor-in-H2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>(31.0482004, 28.4958421)</t>
+          <t>https://globalbiodefense.com/2025/07/23/what-the-who-pandemic-agreement-and-ihr-reforms-mean-for-the-future-of-pandemic-preparedness/</t>
         </is>
       </c>
     </row>
@@ -1502,26 +1415,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran agrees to visit by team from UN nuclear watchdog in coming weeks</t>
+          <t>Africa CDC warns of exponential mpox spread in Guinea</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t xml:space="preserve">Guinea </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Conakry</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45861</v>
+        <v>45863</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1531,7 +1444,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1541,151 +1454,140 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/middle-east/iran-agrees-visit-by-team-un-nuclear-watchdog-coming-weeks-2025-07-23/</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>https://www.cidrap.umn.edu/mpox/africa-cdc-warns-exponential-mpox-spread-guinea</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Blast in Syria’s Idlib kills at least six, injures over 100, state media say</t>
+          <t>Iran and E3 nations agree to resume nuclear talks after no breakthrough in Istanbul</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Idlib</t>
+          <t>Istanbul</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/amp/News/middle-east/2025/07/24/explosion-heard-in-idlib-syrian-media-report</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>(35.8595974, 36.5713701)</t>
+          <t>https://www.euronews.com/my-europe/2025/07/25/iran-and-e3-nations-agree-to-resume-nuclear-talks-after-no-breakthrough-in-istanbul</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blast in Syria’s Idlib kills at least six, injures over 100, state media say</t>
+          <t>Strikes on Iran thwarted fission and fusion nukes, and ‘electronic pulse’ bomb – report</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Idlib</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>45862</v>
+        <v>45864</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/amp/News/middle-east/2025/07/24/explosion-heard-in-idlib-syrian-media-report</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>(35.8595974, 36.5713701)</t>
+          <t>https://www.timesofisrael.com/strikes-on-iran-thwarted-bomb-designed-to-cripple-israel-electronically-report/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Radiation-Resistant Bacterium Discovered in Irradiator Pool Challenges Safety Assumptions</t>
+          <t>NRC Eyes New Accident Tolerant Nuclear Fuels For Commercial Use</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>45860</v>
+        <v>45864</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1695,7 +1597,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1705,43 +1607,38 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/22/radiation-resistant-bacillus-cereus-irradiator-discovery/</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>(34.7811578, 135.4699059)</t>
+          <t>https://www.forbes.com/sites/noelfletcher/2025/07/26/nrc-eyes-new-accident-tolerant-nuclear-fuels-for-commercial-use/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What the WHO Pandemic Agreement and IHR Reforms Mean for the Future of Pandemic Preparedness</t>
+          <t>Update 306 – IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Zaporizhzhia</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>45861</v>
+        <v>45868</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1751,7 +1648,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1761,43 +1658,38 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/23/what-the-who-pandemic-agreement-and-ihr-reforms-mean-for-the-future-of-pandemic-preparedness/</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-306-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Africa CDC warns of exponential mpox spread in Guinea</t>
+          <t>Outlook for Nuclear Energy in Africa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guinea </t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Conakry</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>45863</v>
+        <v>45868</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1807,7 +1699,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1817,12 +1709,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/mpox/africa-cdc-warns-exponential-mpox-spread-guinea</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>(9.5170602, -13.6998434)</t>
+          <t>https://www.iaea.org/publications/15896/outlook-for-nuclear-energy-in-africa</t>
         </is>
       </c>
     </row>
@@ -1839,21 +1726,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran and E3 nations agree to resume nuclear talks after no breakthrough in Istanbul</t>
+          <t>Shipping container-sized nuclear reactor enters build phase to power US military bases</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istanbul</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>45863</v>
+        <v>45869</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1863,7 +1750,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1873,53 +1760,48 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.euronews.com/my-europe/2025/07/25/iran-and-e3-nations-agree-to-resume-nuclear-talks-after-no-breakthrough-in-istanbul</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>(41.335895, 34.0204704)</t>
+          <t>https://interestingengineering.com/energy/nuclear-reactor-fits-inside-container</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Strikes on Iran thwarted fission and fusion nukes, and ‘electronic pulse’ bomb – report</t>
+          <t>Report describes rare type of deadly flu-related brain damage in kids</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>45864</v>
+        <v>45870</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1929,25 +1811,24 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.timesofisrael.com/strikes-on-iran-thwarted-bomb-designed-to-cripple-israel-electronically-report/</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>https://www.cidrap.umn.edu/influenza-general/report-describes-rare-type-deadly-flu-related-brain-damage-kids</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NRC Eyes New Accident Tolerant Nuclear Fuels For Commercial Use</t>
+          <t>NYC health officials report Harlem Legionnaires' outbreak</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1957,21 +1838,21 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45864</v>
+        <v>45869</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1981,43 +1862,38 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/noelfletcher/2025/07/26/nrc-eyes-new-accident-tolerant-nuclear-fuels-for-commercial-use/</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
+          <t>https://www.cidrap.umn.edu/legionella/nyc-health-officials-report-harlem-legionnaires-outbreak</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Update 306 – IAEA Director General Statement on Situation in Ukraine</t>
+          <t>Almost 90% of treated Ebola survivors have long-term health effects, data show</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zaporizhzhia</t>
+          <t>Kinshasa</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45868</v>
+        <v>45869</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2027,7 +1903,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2037,43 +1913,38 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-306-iaea-director-general-statement-on-situation-in-ukraine</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>(47.8507859, 35.1182867)</t>
+          <t>https://www.cidrap.umn.edu/ebola/almost-90-treated-ebola-survivors-have-long-term-health-effects-data-show</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Outlook for Nuclear Energy in Africa</t>
+          <t>Radioactive wasp nest found at old US nuclear weapons site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45868</v>
+        <v>45870</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2083,7 +1954,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2093,12 +1964,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15896/outlook-for-nuclear-energy-in-africa</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://www.bbc.com/news/articles/c3dpxr85228o</t>
         </is>
       </c>
     </row>
@@ -2115,17 +1981,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shipping container-sized nuclear reactor enters build phase to power US military bases</t>
+          <t>Former Iranian foreign minister proposes regional nuclear pact</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
@@ -2139,7 +2005,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2149,29 +2015,24 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/energy/nuclear-reactor-fits-inside-container</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>(38.0410576, -78.5055084)</t>
+          <t>https://www.theguardian.com/world/2025/jul/31/former-iranian-foreign-minister-proposes-regional-nuclear-pact</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Report describes rare type of deadly flu-related brain damage in kids</t>
+          <t>Trump orders two nuclear submarines to be repositioned after former Russian president's comments</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2191,11 +2052,11 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2205,99 +2066,89 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/influenza-general/report-describes-rare-type-deadly-flu-related-brain-damage-kids</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
+          <t>https://www.thenationalnews.com/news/us/2025/08/01/trump-nuclear-submarines-russia/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NYC health officials report Harlem Legionnaires' outbreak</t>
+          <t>Update 307 – IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Zaporizhzhia</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45869</v>
+        <v>45871</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/legionella/nyc-health-officials-report-harlem-legionnaires-outbreak</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>(40.7127281, -74.0060152)</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-307-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Almost 90% of treated Ebola survivors have long-term health effects, data show</t>
+          <t>Evaluation of Physical Protection Systems at Nuclear Facilities</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kinshasa</t>
+          <t>Vienna</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45869</v>
+        <v>45871</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2307,7 +2158,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2317,12 +2168,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/ebola/almost-90-treated-ebola-survivors-have-long-term-health-effects-data-show</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>(-4.32171, 15.3122511)</t>
+          <t>https://www.iaea.org/publications/15745/evaluation-of-physical-protection-systems-at-nuclear-facilities</t>
         </is>
       </c>
     </row>
@@ -2334,26 +2180,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Radioactive wasp nest found at old US nuclear weapons site</t>
+          <t>A Breakthrough in MERS Diagnostics: Scientists Unveil Highly Sensitive Rapid Test</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>45870</v>
+        <v>45867</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2363,7 +2209,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Animal</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2373,12 +2219,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/c3dpxr85228o</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>(18.3640277, -65.9526469)</t>
+          <t>https://globalbiodefense.com/2025/07/29/rapid-mers-test-trf-fluorescence-diagnostic-2025/</t>
         </is>
       </c>
     </row>
@@ -2390,26 +2231,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Former Iranian foreign minister proposes regional nuclear pact</t>
+          <t>Pan-Coronavirus Drug Discovery Gets a Boost from Global AI Blind Challenge</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45869</v>
+        <v>45866</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2419,7 +2260,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2429,25 +2270,24 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/world/2025/jul/31/former-iranian-foreign-minister-proposes-regional-nuclear-pact</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>https://globalbiodefense.com/2025/07/28/pan-coronavirus-ai-drug-discovery-blind-challenge-results/</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trump orders two nuclear submarines to be repositioned after former Russian president's comments</t>
+          <t>Long-Term SARS-CoV-2 Infection in a Person with HIV Offers New Clues to Viral Evolution</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2457,21 +2297,21 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>45870</v>
+        <v>45871</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2481,43 +2321,38 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/news/us/2025/08/01/trump-nuclear-submarines-russia/</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
+          <t>https://globalbiodefense.com/2025/08/02/long-term-sars-cov-2-infection-in-a-person-with-hiv-offers-new-clues-to-viral-evolution/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Update 307 – IAEA Director General Statement on Situation in Ukraine</t>
+          <t>Mpox testing initiative launched in Africa as outbreaks continue</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zaporizhzhia</t>
+          <t>Addis Ababa</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45871</v>
+        <v>45870</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2527,29 +2362,24 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-307-iaea-director-general-statement-on-situation-in-ukraine</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>(47.8507859, 35.1182867)</t>
+          <t>https://www.cidrap.umn.edu/mpox/mpox-testing-initiative-launched-africa-outbreaks-continue</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2559,21 +2389,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Evaluation of Physical Protection Systems at Nuclear Facilities</t>
+          <t>Pakistan supports Iran's right to develop nuclear capability for peaceful purposes</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Vienna</t>
+          <t>Islamabad</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45871</v>
+        <v>45872</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2593,12 +2423,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/publications/15745/evaluation-of-physical-protection-systems-at-nuclear-facilities</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>(48.2083537, 16.3725042)</t>
+          <t>https://economictimes.indiatimes.com/news/defence/pakistan-supports-irans-right-to-develop-nuclear-capability-for-peaceful-purposes/articleshow/123075451.cms?from=mdr</t>
         </is>
       </c>
     </row>
@@ -2610,26 +2435,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>A Breakthrough in MERS Diagnostics: Scientists Unveil Highly Sensitive Rapid Test</t>
+          <t>Ukrainian Intelligence Obtains Secret Data on Knyaz Pozharskiy, Russia’s New Nuclear Submarine</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Kyiev</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45867</v>
+        <v>45872</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2639,7 +2464,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2649,53 +2474,48 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/29/rapid-mers-test-trf-fluorescence-diagnostic-2025/</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>(37.5666791, 126.9782914)</t>
+          <t>https://militarnyi.com/en/news/ukrainian-intelligence-obtains-secret-data-on-knyaz-pozharskiy-russia-s-new-nuclear-submarine/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pan-Coronavirus Drug Discovery Gets a Boost from Global AI Blind Challenge</t>
+          <t>Explosion at anesthetic gas plant in Türkiye kills two workers</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t xml:space="preserve">Tekirdağ </t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45866</v>
+        <v>45872</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human, Infrastructure</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2705,53 +2525,48 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/07/28/pan-coronavirus-ai-drug-discovery-blind-challenge-results/</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://www.azernews.az/region/245522.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Long-Term SARS-CoV-2 Infection in a Person with HIV Offers New Clues to Viral Evolution</t>
+          <t>Explosion Hits Central Asia–Center Gas Pipeline in Southern Russia</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Volgograd</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>45871</v>
+        <v>45872</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2761,43 +2576,38 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/08/02/long-term-sars-cov-2-infection-in-a-person-with-hiv-offers-new-clues-to-viral-evolution/</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>(42.3788774, -72.032366)</t>
+          <t>https://militarnyi.com/en/news/explosion-hits-central-asia-center-gas-pipeline-in-southern-russia/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Mpox testing initiative launched in Africa as outbreaks continue</t>
+          <t>Ukraine drone attack causes fire at Sochi oil depot, Russia says</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Addis Ababa</t>
+          <t>Sochi</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>45870</v>
+        <v>45872</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2807,7 +2617,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2817,12 +2627,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/mpox/mpox-testing-initiative-launched-africa-outbreaks-continue</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>(9.0358287, 38.7524127)</t>
+          <t>https://www.bbc.com/news/articles/ckglyv396ppo</t>
         </is>
       </c>
     </row>
@@ -2834,26 +2639,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pakistan supports Iran's right to develop nuclear capability for peaceful purposes</t>
+          <t>"الطوارئ والأزمات" بأبوظبي تفعل مركز التنسيق والمتابعة بالعين</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Islamabad</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>45872</v>
+        <v>45873</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2863,7 +2668,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2873,12 +2678,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://economictimes.indiatimes.com/news/defence/pakistan-supports-irans-right-to-develop-nuclear-capability-for-peaceful-purposes/articleshow/123075451.cms?from=mdr</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>(33.6938118, 73.0651511)</t>
+          <t>https://www.wam.ae/ar/article/bl0ymxo-%D8%A7%D9%84%D8%B7%D9%88%D8%A7%D8%B1%D8%A6-%D9%88%D8%A7%D9%84%D8%A3%D8%B2%D9%85%D8%A7%D8%AA-%D8%A8%D8%A3%D8%A8%D9%88%D8%B8%D8%A8%D9%8A-%D8%AA%D9%81%D8%B9%D9%84-%D9%85%D8%B1%D9%83%D8%B2-%D8%A7%D9%84%D8%AA%D9%86%D8%B3%D9%8A%D9%82</t>
         </is>
       </c>
     </row>
@@ -2895,21 +2695,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ukrainian Intelligence Obtains Secret Data on Knyaz Pozharskiy, Russia’s New Nuclear Submarine</t>
+          <t>Iran affirms commitment to nuclear deal; rejects Europe's 'Trigger Mechanism'</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kyiev</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>45872</v>
+        <v>45873</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2919,7 +2719,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2929,53 +2729,48 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://militarnyi.com/en/news/ukrainian-intelligence-obtains-secret-data-on-knyaz-pozharskiy-russia-s-new-nuclear-submarine/</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>(50.4500336, 30.5241361)</t>
+          <t>https://www.wam.ae/en/article/bl0yv7e-iran-affirms-commitment-nuclear-deal-rejects</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Explosion at anesthetic gas plant in Türkiye kills two workers</t>
+          <t>US engineer explores sponge-like nuclear reactor shield to resist earthquakes</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tekirdağ </t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>45872</v>
+        <v>45874</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2985,53 +2780,48 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.azernews.az/region/245522.html</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>(41.0731403, 27.4102013)</t>
+          <t>https://interestingengineering.com/energy/earthquake-proof-nuclear-reactor-sheild</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Explosion at anesthetic gas plant in Türkiye kills two workers</t>
+          <t>NASA could deploy 100-kilowatt nuclear reactor on Moon to outpace China, Russia</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tekirdağ </t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>45872</v>
+        <v>45874</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3041,43 +2831,38 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.azernews.az/region/245522.html</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>(41.0731403, 27.4102013)</t>
+          <t>https://interestingengineering.com/energy/nasa-could-deploy-moon-reactor-2030</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Explosion Hits Central Asia–Center Gas Pipeline in Southern Russia</t>
+          <t>Emerging from the Unknowing: WHO India’s strategic response to the pandemic</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Volgograd</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>45872</v>
+        <v>45874</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3087,7 +2872,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3097,43 +2882,38 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://militarnyi.com/en/news/explosion-hits-central-asia-center-gas-pipeline-in-southern-russia/</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>(48.7081906, 44.5153353)</t>
+          <t>https://www.who.int/publications/i/item/9789290221005</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ukraine drone attack causes fire at Sochi oil depot, Russia says</t>
+          <t>Report of the sixth, seventh and eighth meetings of the Technical Advisory Group on Malaria Elimination and Certification: 20 March, 9–10 September and 3–4 December 2024</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochi</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45872</v>
+        <v>45873</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3143,7 +2923,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3153,39 +2933,34 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.bbc.com/news/articles/ckglyv396ppo</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>(43.5854823, 39.723109)</t>
+          <t>https://www.who.int/publications/i/item/9789240113459</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>"الطوارئ والأزمات" بأبوظبي تفعل مركز التنسيق والمتابعة بالعين</t>
+          <t>A framework for civil society organization engagement in health emergencies</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3209,12 +2984,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/ar/article/bl0ymxo-%D8%A7%D9%84%D8%B7%D9%88%D8%A7%D8%B1%D8%A6-%D9%88%D8%A7%D9%84%D8%A3%D8%B2%D9%85%D8%A7%D8%AA-%D8%A8%D8%A3%D8%A8%D9%88%D8%B8%D8%A8%D9%8A-%D8%AA%D9%81%D8%B9%D9%84-%D9%85%D8%B1%D9%83%D8%B2-%D8%A7%D9%84%D8%AA%D9%86%D8%B3%D9%8A%D9%82</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>(24.3564023, 54.6898984)</t>
+          <t>https://www.who.int/publications/i/item/9789240109520</t>
         </is>
       </c>
     </row>
@@ -3231,21 +3001,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iran affirms commitment to nuclear deal; rejects Europe's 'Trigger Mechanism'</t>
+          <t>Tritium Level Far Below Japan’s Operational Limit in 14th Batch of ALPS-Treated Water, IAEA Confirms</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Fukushima</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45873</v>
+        <v>45876</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3255,7 +3025,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3265,15 +3035,14 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.wam.ae/en/article/bl0yv7e-iran-affirms-commitment-nuclear-deal-rejects</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>https://www.iaea.org/newscenter/pressreleases/tritium-level-far-below-japans-operational-limit-in-14th-batch-of-alps-treated-water-iaea-confirms</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3283,21 +3052,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US engineer explores sponge-like nuclear reactor shield to resist earthquakes</t>
+          <t>Update 308 – IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>Zaporizhzhia</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3307,7 +3076,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3317,12 +3086,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/energy/earthquake-proof-nuclear-reactor-sheild</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>(43.1700264, -107.568534)</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-308-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
@@ -3339,21 +3103,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NASA could deploy 100-kilowatt nuclear reactor on Moon to outpace China, Russia</t>
+          <t>Legislation In South Korea Will Create ‘Investable Framework’ For Small Modular Reactors</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>45874</v>
+        <v>45876</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3363,7 +3127,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3373,43 +3137,38 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://interestingengineering.com/energy/nasa-could-deploy-moon-reactor-2030</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
+          <t>https://www.nucnet.org/news/legislation-in-south-korea-will-create-investable-framework-for-small-modular-reactors-8-4-2025</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Emerging from the Unknowing: WHO India’s strategic response to the pandemic</t>
+          <t>General Matter Announces Plans For $1.5 Billion Uranium Enrichment Facility At Paducah</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3419,7 +3178,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3429,43 +3188,38 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/9789290221005</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>(17.9881649, 77.0972593)</t>
+          <t>https://www.nucnet.org/news/general-matter-announces-plans-for-usd1-5-billion-uranium-enrichment-facility-at-paducah-8-3-2025</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Report of the sixth, seventh and eighth meetings of the Technical Advisory Group on Malaria Elimination and Certification: 20 March, 9–10 September and 3–4 December 2024</t>
+          <t>Laos Looks To Russia As It Joins Southeast Asian Nations Planning For Nuclear</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Vientiane</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>45873</v>
+        <v>45875</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3475,7 +3229,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3485,19 +3239,14 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/9789240113459</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.nucnet.org/news/laos-looks-to-russia-for-development-of-nuclear-power-8-3-2025</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3507,21 +3256,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>A framework for civil society organization engagement in health emergencies</t>
+          <t>Cambodia announces 15th human H5N1 infection of the year</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Phnom Penh</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>45873</v>
+        <v>45875</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -3531,7 +3280,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3541,12 +3290,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/9789240109520</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.cidrap.umn.edu/avian-influenza-bird-flu/cambodia-announces-15th-human-h5n1-infection-year</t>
         </is>
       </c>
     </row>
@@ -3558,58 +3302,53 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tritium Level Far Below Japan’s Operational Limit in 14th Batch of ALPS-Treated Water, IAEA Confirms</t>
+          <t>China fights mosquito-borne chikungunya virus with drones, fines and nets as thousands fall ill</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fukushima</t>
+          <t>Foshan</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>45876</v>
+        <v>45875</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/tritium-level-far-below-japans-operational-limit-in-14th-batch-of-alps-treated-water-iaea-confirms</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>(35.9263502, 136.6068127)</t>
+          <t>https://apnews.com/article/china-chikungunya-virus-outbreak-control-measures-3ee97c21152b05ed0912af646594eafd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3619,21 +3358,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Update 308 – IAEA Director General Statement on Situation in Ukraine</t>
+          <t>NEA and Korea’s Ministry of Trade, Industry and Energy to co-host high-level conference on advancing nuclear new build</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>France</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zaporizhzhia</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45875</v>
+        <v>45876</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -3653,12 +3392,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-308-iaea-director-general-statement-on-situation-in-ukraine</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>(47.8507859, 35.1182867)</t>
+          <t>https://www.oecd-nea.org/jcms/pl_108691/nea-and-korea-s-ministry-of-trade-industry-and-energy-to-co-host-high-level-conference-on-advancing-nuclear-new-build</t>
         </is>
       </c>
     </row>
@@ -3675,17 +3409,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Legislation In South Korea Will Create ‘Investable Framework’ For Small Modular Reactors</t>
+          <t>Denver airport contemplating onsite reactor</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
@@ -3709,12 +3443,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/legislation-in-south-korea-will-create-investable-framework-for-small-modular-reactors-8-4-2025</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>(37.5666791, 126.9782914)</t>
+          <t>https://world-nuclear-news.org/articles/denver-airport-contemplating-onsite-reactor</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3460,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>General Matter Announces Plans For $1.5 Billion Uranium Enrichment Facility At Paducah</t>
+          <t>Chinese cyberattack on US nuclear agency highlights importance of cyber hygiene</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3741,11 +3470,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45875</v>
+        <v>45877</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3760,17 +3489,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/general-matter-announces-plans-for-usd1-5-billion-uranium-enrichment-facility-at-paducah-8-3-2025</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>(40.1885761, -85.1314849)</t>
+          <t>https://www.aspistrategist.org.au/chinese-cyberattack-on-us-nuclear-agency-highlights-importance-of-cyber-hygiene/</t>
         </is>
       </c>
     </row>
@@ -3787,17 +3511,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Laos Looks To Russia As It Joins Southeast Asian Nations Planning For Nuclear</t>
+          <t xml:space="preserve">Russia nuclear submarine base damaged after earthquake </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vientiane</t>
+          <t xml:space="preserve">Kamchatka </t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -3821,43 +3545,38 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.nucnet.org/news/laos-looks-to-russia-for-development-of-nuclear-power-8-3-2025</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>(17.9640988, 102.6133707)</t>
+          <t>https://www.theguardian.com/world/2025/aug/06/russia-nuclear-submarine-base-earthquake-damage-rybachiy-kamchatka</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cambodia announces 15th human H5N1 infection of the year</t>
+          <t>Iranian Nuclear Scientists Sought Sensitive Tech During Secret Russia Visit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Phnom Penh</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45875</v>
+        <v>45874</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3867,22 +3586,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/avian-influenza-bird-flu/cambodia-announces-15th-human-h5n1-infection-year</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>(11.5730391, 104.857807)</t>
+          <t>https://www.themoscowtimes.com/2025/08/05/iranian-nuclear-scientists-sought-sensitive-tech-during-secret-russia-visit-ft-a90105</t>
         </is>
       </c>
     </row>
@@ -3894,82 +3608,77 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical, Biological, Radiological, Nuclear</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>China fights mosquito-borne chikungunya virus with drones, fines and nets as thousands fall ill</t>
+          <t>Tajikistan launches new radiation mapping laboratory to boost national safety</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Foshan</t>
+          <t>Dushanbe</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>45875</v>
+        <v>45877</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/china-chikungunya-virus-outbreak-control-measures-3ee97c21152b05ed0912af646594eafd</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>(23.0239788, 113.1159558)</t>
+          <t>https://asiaplustj.info/en/news/tajikistan/security/20250808/tajikistan-launches-new-radiation-mapping-laboratory-to-boost-national-safety</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NEA and Korea’s Ministry of Trade, Industry and Energy to co-host high-level conference on advancing nuclear new build</t>
+          <t>Dutch Intelligence Confirms Russia Increasing Use of Chemical Weapons in Ukraine</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Kyiev</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45876</v>
+        <v>45875</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -3979,7 +3688,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human, Weapon</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -3989,43 +3698,38 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.oecd-nea.org/jcms/pl_108691/nea-and-korea-s-ministry-of-trade-industry-and-energy-to-co-host-high-level-conference-on-advancing-nuclear-new-build</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>(48.9759637, 2.1998877)</t>
+          <t>https://uatv.ua/en/dutch-intelligence-confirms-russia-increasing-use-of-chemical-weapons-in-ukraine/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical, Explosive</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver airport contemplating onsite reactor</t>
+          <t>Three workers killed in water tank explosion at Mina Abdullah</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Kuwait City</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45876</v>
+        <v>45874</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -4035,7 +3739,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4045,10 +3749,9 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://world-nuclear-news.org/articles/denver-airport-contemplating-onsite-reactor</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>https://gulfnews.com/world/gulf/kuwait/kuwait-three-expat-workers-killed-in-water-tank-explosion-at-mina-abdullah-1.500222929</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4063,21 +3766,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chinese cyberattack on US nuclear agency highlights importance of cyber hygiene</t>
+          <t>Iran moves surviving nuclear scientists to safe houses</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Washington D.C.</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45877</v>
+        <v>45878</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -4087,22 +3790,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.aspistrategist.org.au/chinese-cyberattack-on-us-nuclear-agency-highlights-importance-of-cyber-hygiene/</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
+          <t>https://www.iranintl.com/en/202508097709</t>
         </is>
       </c>
     </row>
@@ -4114,26 +3812,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Russia nuclear submarine base damaged after earthquake </t>
+          <t>Radioactive water from UK nuclear bomb base leaked into sea, files show</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kamchatka </t>
+          <t>Glasgow</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45875</v>
+        <v>45878</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4143,101 +3841,95 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/world/2025/aug/06/russia-nuclear-submarine-base-earthquake-damage-rybachiy-kamchatka</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>(57.1914882, 160.0383819)</t>
+          <t>https://www.theguardian.com/environment/2025/aug/09/radioactive-water-bomb-base-scotland-leak-sea-files</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Iranian Nuclear Scientists Sought Sensitive Tech During Secret Russia Visit</t>
+          <t>Explosion at Lebanese arms depot kills 6 army experts, wounds several others</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Beirut</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45874</v>
+        <v>45879</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.themoscowtimes.com/2025/08/05/iranian-nuclear-scientists-sought-sensitive-tech-during-secret-russia-visit-ft-a90105</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+          <t>https://apnews.com/article/lebanon-soldiers-killed-zibqin-arms-depot-hezbollah-israel-b7e8b68f7bad3b9010ffd60b59e4e79d</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tajikistan launches new radiation mapping laboratory to boost national safety</t>
+          <t>Immunologic study shows rebound of other viruses after COVID measures lifted</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dushanbe</t>
+          <t>Colorado</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -4251,7 +3943,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4261,19 +3953,14 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://asiaplustj.info/en/news/tajikistan/security/20250808/tajikistan-launches-new-radiation-mapping-laboratory-to-boost-national-safety</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>(38.5856814, 68.760331)</t>
+          <t>https://www.cidrap.umn.edu/covid-19/immunologic-study-shows-rebound-other-viruses-after-covid-measures-lifted</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4283,21 +3970,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tajikistan launches new radiation mapping laboratory to boost national safety</t>
+          <t>UNIDIR Unveils Strategy to Bolster Biosecurity Awareness Among Scientists</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dushanbe</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>45877</v>
+        <v>45875</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -4307,7 +3994,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4317,12 +4004,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://asiaplustj.info/en/news/tajikistan/security/20250808/tajikistan-launches-new-radiation-mapping-laboratory-to-boost-national-safety</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>(38.5856814, 68.760331)</t>
+          <t>https://globalbiodefense.com/2025/08/06/unidir-unveils-strategy-to-bolster-biosecurity-awareness-among-scientists/</t>
         </is>
       </c>
     </row>
@@ -4334,26 +4016,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tajikistan launches new radiation mapping laboratory to boost national safety</t>
+          <t>Russia Officially Ends Commitment to 1987 INF Nuclear Arms Treaty</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dushanbe</t>
+          <t>Moscow</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45877</v>
+        <v>45874</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -4363,22 +4045,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://asiaplustj.info/en/news/tajikistan/security/20250808/tajikistan-launches-new-radiation-mapping-laboratory-to-boost-national-safety</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>(38.5856814, 68.760331)</t>
+          <t>https://www.newsonair.gov.in/russia-officially-ends-commitment-to-1987-inf-nuclear-arms-treaty/</t>
         </is>
       </c>
     </row>
@@ -4390,22 +4067,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tajikistan launches new radiation mapping laboratory to boost national safety</t>
+          <t>Current Epidemic Trends (Based on Rt) for States</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dushanbe</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
@@ -4419,7 +4096,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4429,43 +4106,38 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://asiaplustj.info/en/news/tajikistan/security/20250808/tajikistan-launches-new-radiation-mapping-laboratory-to-boost-national-safety</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>(38.5856814, 68.760331)</t>
+          <t>https://www.cdc.gov/cfa-modeling-and-forecasting/rt-estimates/index.html</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dutch Intelligence Confirms Russia Increasing Use of Chemical Weapons in Ukraine</t>
+          <t>Researchers find signs of regional spread of drug-resistant malaria in Africa</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Zanzibar</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kyiev</t>
+          <t>Zanzibar</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45875</v>
+        <v>45883</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4485,43 +4157,38 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://uatv.ua/en/dutch-intelligence-confirms-russia-increasing-use-of-chemical-weapons-in-ukraine/</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>(50.4500336, 30.5241361)</t>
+          <t>https://www.cidrap.umn.edu/malaria/researchers-find-signs-regional-spread-drug-resistant-malaria-africa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dutch Intelligence Confirms Russia Increasing Use of Chemical Weapons in Ukraine</t>
+          <t>WHO guidelines for malaria</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kyiev</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45875</v>
+        <v>45882</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -4531,7 +4198,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4541,43 +4208,38 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://uatv.ua/en/dutch-intelligence-confirms-russia-increasing-use-of-chemical-weapons-in-ukraine/</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>(50.4500336, 30.5241361)</t>
+          <t>https://www.who.int/publications/i/item/guidelines-for-malaria</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Three workers killed in water tank explosion at Mina Abdullah</t>
+          <t>Biological Weapons Convention: Sixth Session Addresses Verification and Biosecurity</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45874</v>
+        <v>45880</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -4587,7 +4249,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4597,43 +4259,38 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://gulfnews.com/world/gulf/kuwait/kuwait-three-expat-workers-killed-in-water-tank-explosion-at-mina-abdullah-1.500222929</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>(29.3796532, 47.9734174)</t>
+          <t>https://globalbiodefense.com/2025/08/11/biological-weapons-convention-sixth-session-addresses-verification-and-biosecurity/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Three workers killed in water tank explosion at Mina Abdullah</t>
+          <t>China says it ‘opposes’ European sanctions over Iran nuclear program</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kuwait City</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -4643,7 +4300,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4653,19 +4310,14 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://gulfnews.com/world/gulf/kuwait/kuwait-three-expat-workers-killed-in-water-tank-explosion-at-mina-abdullah-1.500222929</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>(29.3796532, 47.9734174)</t>
+          <t>https://english.alarabiya.net/News/middle-east/2025/08/15/china-says-it-opposes-european-sanctions-over-iran-nuclear-program</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4675,21 +4327,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Iran moves surviving nuclear scientists to safe houses</t>
+          <t>Russia says it prevented Ukrainian drone attack on Smolensk nuclear power plant</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Smolensk</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45878</v>
+        <v>45886</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -4699,49 +4351,48 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.iranintl.com/en/202508097709</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+          <t>https://www.thehindu.com/news/international/russia-says-it-prevented-ukrainian-drone-attack-on-smolensk-nuclear-power-plant/article69944057.ece#goog_rewarded</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Radioactive water from UK nuclear bomb base leaked into sea, files show</t>
+          <t>Explosion rocks New York apartment block, fire erupts</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Glasgow</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45878</v>
+        <v>45885</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -4751,63 +4402,58 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/environment/2025/aug/09/radioactive-water-bomb-base-scotland-leak-sea-files</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>(55.9342865, -4.689854)</t>
+          <t>https://gulfnews.com/world/americas/explosion-rocks-new-york-apartment-block-fire-erupts-1.500234998</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Explosion at Lebanese arms depot kills 6 army experts, wounds several others</t>
+          <t>OU Researcher Advances Tools to Monitor Radioactive Pollution</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Beirut</t>
+          <t>Oklahoma</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45879</v>
+        <v>45884</v>
       </c>
       <c r="G79" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4817,43 +4463,38 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/lebanon-soldiers-killed-zibqin-arms-depot-hezbollah-israel-b7e8b68f7bad3b9010ffd60b59e4e79d</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>(33.8892265, 35.5025585)</t>
+          <t>https://ou.edu/news/articles/2025/august/ou-researcher-tools-monitor-radioactive-pollution</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Immunologic study shows rebound of other viruses after COVID measures lifted</t>
+          <t>Battery explosion possibly behind Seoul apartment blaze that killed 2, injured 13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -4863,7 +4504,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4873,39 +4514,38 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/covid-19/immunologic-study-shows-rebound-other-viruses-after-covid-measures-lifted</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+          <t>https://koreajoongangdaily.joins.com/news/2025-08-18/national/socialAffairs/Battery-explosion-possibly-behind-Seoul-apartment-blaze-that-killed-2-injured-13/2377707</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UNIDIR Unveils Strategy to Bolster Biosecurity Awareness Among Scientists</t>
+          <t>New construction at rumored North Korean nuclear site renews concerns over aims</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Pyongyang</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>45875</v>
+        <v>45887</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -4915,7 +4555,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4925,43 +4565,38 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/08/06/unidir-unveils-strategy-to-bolster-biosecurity-awareness-among-scientists/</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.nknews.org/pro/new-construction-at-rumored-north-korean-nuclear-site-renews-concerns-over-aims/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Russia Officially Ends Commitment to 1987 INF Nuclear Arms Treaty</t>
+          <t>Tenth Meeting of the WHO South-East Asia Regional Verification Commission for Measles and Rubella Elimination</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Moscow</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45874</v>
+        <v>45887</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4971,29 +4606,24 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/russia-officially-ends-commitment-to-1987-inf-nuclear-arms-treaty/</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>(55.625578, 37.6063916)</t>
+          <t>https://www.who.int/publications/i/item/sea-immun-174</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5003,21 +4633,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Current Epidemic Trends (Based on Rt) for States</t>
+          <t>Seventeenth Biregional Meeting of National Influenza Centres and Influenza Surveillance in WHO’s South-East Asia and Western Pacific Regions, Manila, Philippines, 20-22 November 2024</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>45877</v>
+        <v>45887</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -5037,19 +4667,14 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/cfa-modeling-and-forecasting/rt-estimates/index.html</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://www.who.int/publications/i/item/RS-2024-GE-45</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5059,27 +4684,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Researchers find signs of regional spread of drug-resistant malaria in Africa</t>
+          <t>New Jersey officials probe local malaria infection</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Zanzibar</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Zanzibar</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45883</v>
+        <v>45888</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -5093,43 +4718,38 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/malaria/researchers-find-signs-regional-spread-drug-resistant-malaria-africa</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>(-6.1664908, 39.2074312)</t>
+          <t>https://www.cidrap.umn.edu/malaria/new-jersey-officials-probe-local-malaria-infection</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>WHO guidelines for malaria</t>
+          <t>North Korea's Kim calls for rapid nuclear buildup</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>North Korea</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Pyongyang</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>45882</v>
+        <v>45888</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5139,7 +4759,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5149,43 +4769,38 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/guidelines-for-malaria</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.reuters.com/world/asia-pacific/north-koreas-kim-calls-rapid-nuclear-buildup-amid-us-south-korea-exercises-2025-08-18/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Biological Weapons Convention: Sixth Session Addresses Verification and Biosecurity</t>
+          <t>Google announces Tennessee as site for small modular nuclear reactor</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>45880</v>
+        <v>45888</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -5195,7 +4810,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5205,19 +4820,14 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://globalbiodefense.com/2025/08/11/biological-weapons-convention-sixth-session-addresses-verification-and-biosecurity/</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.reuters.com/sustainability/boards-policy-regulation/google-announces-tennessee-site-small-modular-nuclear-reactor-2025-08-18/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5227,21 +4837,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>China says it ‘opposes’ European sanctions over Iran nuclear program</t>
+          <t>Software modeling to validate the safety of nuclear disposal sites</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>45884</v>
+        <v>45887</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -5251,7 +4861,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5261,19 +4871,14 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/middle-east/2025/08/15/china-says-it-opposes-european-sanctions-over-iran-nuclear-program</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>(22.2088246, 107.2173992)</t>
+          <t>https://www.ans.org/news/article-7284/software-modeling-to-validate-the-safety-of-nuclear-disposal-sites/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5283,21 +4888,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Russia says it prevented Ukrainian drone attack on Smolensk nuclear power plant</t>
+          <t>Iran to begin new round of talks with UN nuclear watchdog in upcoming days</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Smolensk</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5312,34 +4917,29 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/international/russia-says-it-prevented-ukrainian-drone-attack-on-smolensk-nuclear-power-plant/article69944057.ece#goog_rewarded</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>(54.77897, 32.0471812)</t>
+          <t>https://www.aa.com.tr/en/middle-east/iran-to-begin-new-round-of-talks-with-un-nuclear-watchdog-in-upcoming-days/3662361</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Chemical, Biological, Radiological, Nuclear</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Explosion rocks New York apartment block, fire erupts</t>
+          <t>South Carolina Firm to Equip CBRN Gears With Anti-Hazard Fabric Tech</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5349,11 +4949,11 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>South Carolina</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>45885</v>
+        <v>45887</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -5363,7 +4963,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5373,12 +4973,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://gulfnews.com/world/americas/explosion-rocks-new-york-apartment-block-fire-erupts-1.500234998</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>(40.7127281, -74.0060152)</t>
+          <t>https://thedefensepost.com/2025/08/18/us-hazard-fabric-gear/</t>
         </is>
       </c>
     </row>
@@ -5390,26 +4985,26 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OU Researcher Advances Tools to Monitor Radioactive Pollution</t>
+          <t>Hong Kong to use robot dogs to fight mosquito-borne virus</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>45884</v>
+        <v>45888</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5429,39 +5024,34 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://ou.edu/news/articles/2025/august/ou-researcher-tools-monitor-radioactive-pollution</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>(34.9550817, -97.2684063)</t>
+          <t>https://telegrafi.com/en/Hong-Kong-to-use-robot-dogs-to-fight-mosquito-borne-virus/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Battery explosion possibly behind Seoul apartment blaze that killed 2, injured 13</t>
+          <t>Laboratory reagent contamination threatens accuracy of infectious disease research</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Seoul</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
@@ -5475,7 +5065,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5485,43 +5075,38 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://koreajoongangdaily.joins.com/news/2025-08-18/national/socialAffairs/Battery-explosion-possibly-behind-Seoul-apartment-blaze-that-killed-2-injured-13/2377707</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>(37.5666791, 126.9782914)</t>
+          <t>https://www.news-medical.net/news/20250818/Laboratory-reagent-contamination-threatens-accuracy-of-infectious-disease-research.aspx</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Explosive</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New construction at rumored North Korean nuclear site renews concerns over aims</t>
+          <t>Explosion rocks cargo ship near Baltimore bridge collapse site</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Pyongyang</t>
+          <t>Baltimore</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -5541,43 +5126,38 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.nknews.org/pro/new-construction-at-rumored-north-korean-nuclear-site-renews-concerns-over-aims/</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>(39.0167979, 125.7473609)</t>
+          <t>https://gulfnews.com/world/americas/explosion-rocks-cargo-ship-near-baltimore-bridge-collapse-site-1.500237521</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tenth Meeting of the WHO South-East Asia Regional Verification Commission for Measles and Rubella Elimination</t>
+          <t>IAEA monitors Zaporizhia cooling</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Zaporizhzhia</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>45887</v>
+        <v>45889</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -5587,7 +5167,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5597,43 +5177,38 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/sea-immun-174</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.neimagazine.com/news/iaea-monitors-zaporizhia-cooling/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seventeenth Biregional Meeting of National Influenza Centres and Influenza Surveillance in WHO’s South-East Asia and Western Pacific Regions, Manila, Philippines, 20-22 November 2024</t>
+          <t>Iran says it cannot completely cut ties with IAEA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>45887</v>
+        <v>45889</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -5643,7 +5218,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5653,53 +5228,48 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.who.int/publications/i/item/RS-2024-GE-45</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://english.alarabiya.net/News/middle-east/2025/08/20/iran-says-it-cannot-completely-cut-ties-with-iaea</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New Jersey officials probe local malaria infection</t>
+          <t>India ‘successfully tests’ nuclear-capable missile able to reach deep into China</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New Jersey</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5709,12 +5279,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.cidrap.umn.edu/malaria/new-jersey-officials-probe-local-malaria-infection</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>(29.0258132, -80.9271271)</t>
+          <t>https://www.theguardian.com/world/2025/aug/20/india-successfully-tests-nuclear-capable-missile-able-to-reach-deep-into-china</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5296,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>North Korea's Kim calls for rapid nuclear buildup</t>
+          <t>Secret North Korean missile base near China could house nuclear ICBMs, report warns</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5745,7 +5310,7 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>45888</v>
+        <v>45890</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -5765,19 +5330,14 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/world/asia-pacific/north-koreas-kim-calls-rapid-nuclear-buildup-amid-us-south-korea-exercises-2025-08-18/</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>(39.0167979, 125.7473609)</t>
+          <t>https://trt.global/world/article/2bdb276091d5</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>MoU</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5787,21 +5347,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Google announces Tennessee as site for small modular nuclear reactor</t>
+          <t>Blykalla and Research Institutes of Sweden partner on SMRs</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -5821,43 +5381,38 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.reuters.com/sustainability/boards-policy-regulation/google-announces-tennessee-site-small-modular-nuclear-reactor-2025-08-18/</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>(33.6874388, -80.4363743)</t>
+          <t>https://www.world-nuclear-news.org/articles/blykalla-and-research-institutes-of-sweden-partnership</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Software modeling to validate the safety of nuclear disposal sites</t>
+          <t>Thai army confirms white phosphorus use in border fighting</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>45887</v>
+        <v>45889</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -5867,53 +5422,48 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.ans.org/news/article-7284/software-modeling-to-validate-the-safety-of-nuclear-disposal-sites/</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>(42.3788774, -72.032366)</t>
+          <t>https://www.intellinews.com/thai-army-confirms-white-phosphorus-use-in-border-fighting-396974/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Iran to begin new round of talks with UN nuclear watchdog in upcoming days</t>
+          <t>Respiratory Virus Surveillance in the WHO African Region Epidemiological Week 34, August 19 to 25 2024</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Geneve</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>45887</v>
+        <v>45889</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -5923,7 +5473,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5933,39 +5483,38 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.aa.com.tr/en/middle-east/iran-to-begin-new-round-of-talks-with-un-nuclear-watchdog-in-upcoming-days/3662361</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+          <t>https://www.afro.who.int/publications/respiratory-virus-surveillance-who-african-region-epidemiological-week-34-august-19-25</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>South Carolina Firm to Equip CBRN Gears With Anti-Hazard Fabric Tech</t>
+          <t>Artificial intelligence tool for cassava viral diseases diagnosis using participatory surveillance in Burkina FasoProvisionally accepted</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Ouagadougou</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>45887</v>
+        <v>45889</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -5975,7 +5524,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5985,12 +5534,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://thedefensepost.com/2025/08/18/us-hazard-fabric-gear/</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>(18.3640277, -65.9526469)</t>
+          <t>https://www.frontiersin.org/journals/sustainable-food-systems/articles/10.3389/fsufs.2025.1597039/abstract</t>
         </is>
       </c>
     </row>
@@ -6007,7 +5551,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South Carolina Firm to Equip CBRN Gears With Anti-Hazard Fabric Tech</t>
+          <t>CDC Outbreak Communications Toolkit</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6017,11 +5561,11 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -6041,12 +5585,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://thedefensepost.com/2025/08/18/us-hazard-fabric-gear/</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>(18.3640277, -65.9526469)</t>
+          <t>https://www.cdc.gov/west-nile-virus/php/outbreak-communication/index.html</t>
         </is>
       </c>
     </row>
@@ -6058,12 +5597,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Biological</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>South Carolina Firm to Equip CBRN Gears With Anti-Hazard Fabric Tech</t>
+          <t>Machine learning model maps West Nile virus risk in Northeast US</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6073,11 +5612,11 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>45887</v>
+        <v>45888</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -6087,7 +5626,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human, Technology</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6097,12 +5636,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>https://thedefensepost.com/2025/08/18/us-hazard-fabric-gear/</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>(18.3640277, -65.9526469)</t>
+          <t>https://medicalxpress.com/news/2025-08-machine-west-nile-virus-northeast.html</t>
         </is>
       </c>
     </row>
@@ -6119,21 +5653,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>South Carolina Firm to Equip CBRN Gears With Anti-Hazard Fabric Tech</t>
+          <t>Iran says it cannot completely cut ties with IAEA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Tehran</t>
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>45887</v>
+        <v>45889</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -6143,7 +5677,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6153,43 +5687,38 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>https://thedefensepost.com/2025/08/18/us-hazard-fabric-gear/</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>(18.3640277, -65.9526469)</t>
+          <t>https://english.alarabiya.net/News/middle-east/2025/08/20/iran-says-it-cannot-completely-cut-ties-with-iaea</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Exercise</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hong Kong to use robot dogs to fight mosquito-borne virus</t>
+          <t>U.S. Army taps INL’s nuclear expertise, capabilities to strengthen radiological response and readiness</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Idaho</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6199,7 +5728,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6209,43 +5738,38 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>https://telegrafi.com/en/Hong-Kong-to-use-robot-dogs-to-fight-mosquito-borne-virus/</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>(31.2098936, 121.313029)</t>
+          <t>https://inl.gov/feature-story/u-s-army-taps-inls-nuclear-expertise-capabilities-to-strengthen-radiological-response-and-readiness/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear, Radiological</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Laboratory reagent contamination threatens accuracy of infectious disease research</t>
+          <t>Enhancing Radiological Data Exchange and Strengthening Cooperation in Nuclear Safety between the EU and the Western Balkans</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Brussels</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>45887</v>
+        <v>45889</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6255,7 +5779,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6265,43 +5789,38 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>https://www.news-medical.net/news/20250818/Laboratory-reagent-contamination-threatens-accuracy-of-infectious-disease-research.aspx</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>(22.2088246, 107.2173992)</t>
+          <t>https://enlargement.ec.europa.eu/news/enhancing-radiological-data-exchange-and-strengthening-cooperation-nuclear-safety-between-eu-and-2025-08-20_en</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Explosive</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Explosion rocks cargo ship near Baltimore bridge collapse site</t>
+          <t>Japan and South Korea Reportedly Consider Nuclear Weapons Amid Regional Threats</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan, South Korea</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Baltimore</t>
+          <t>Tokyo, Seoul</t>
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -6311,49 +5830,44 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>https://gulfnews.com/world/americas/explosion-rocks-cargo-ship-near-baltimore-bridge-collapse-site-1.500237521</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>(39.2908816, -76.610759)</t>
+          <t>https://united24media.com/latest-news/japan-and-south-korea-reportedly-consider-nuclear-weapons-amid-regional-threats-10931</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Radiological</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IAEA monitors Zaporizhia cooling</t>
+          <t>Walmart Recalls Frozen Shrimp After Radioactive Contamination Warning</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zaporizhzhia</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
@@ -6367,29 +5881,24 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>https://www.neimagazine.com/news/iaea-monitors-zaporizhia-cooling/</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>(47.8507859, 35.1182867)</t>
+          <t>https://www.nytimes.com/2025/08/20/business/radioactive-shrimp-walmart-recall.html</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Exercise</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6399,17 +5908,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Iran says it cannot completely cut ties with IAEA</t>
+          <t>Jordan Enhances Nuclear Emergency Readiness Through "Dragon Eye" Exercise</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Petra</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
@@ -6423,7 +5932,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6433,15 +5942,14 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>https://english.alarabiya.net/News/middle-east/2025/08/20/iran-says-it-cannot-completely-cut-ties-with-iaea</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
+          <t>https://www.petra.gov.jo/Include/InnerPage.jsp?ID=74765&amp;lang=en&amp;name=en_news</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6451,21 +5959,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>India ‘successfully tests’ nuclear-capable missile able to reach deep into China</t>
+          <t>Smoke prompts automatic shutdown at Busan's Shin-Kori Unit 1 nuclear plant</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Busan</t>
         </is>
       </c>
       <c r="F109" s="2" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -6475,7 +5983,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6485,12 +5993,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>https://www.theguardian.com/world/2025/aug/20/india-successfully-tests-nuclear-capable-missile-able-to-reach-deep-into-china</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>(17.9881649, 77.0972593)</t>
+          <t>https://biz.chosun.com/en/en-industry/2025/08/21/O4HNPSXHBBHIDOLES2AGR2CXTM/</t>
         </is>
       </c>
     </row>
@@ -6507,21 +6010,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Secret North Korean missile base near China could house nuclear ICBMs, report warns</t>
+          <t>Italy Boosts Security at Aviano US Nuclear Base Amid Russian Sabotage Fears</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>North Korea</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pyongyang</t>
+          <t xml:space="preserve">Aviano </t>
         </is>
       </c>
       <c r="F110" s="2" t="n">
-        <v>45890</v>
+        <v>45888</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -6541,39 +6044,34 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>https://trt.global/world/article/2bdb276091d5</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>(39.0167979, 125.7473609)</t>
+          <t>https://thedefensepost.com/2025/08/19/italy-us-nuclear-russia/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Mou</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical, Biological, Radiological, Nuclear</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Blykalla and Research Institutes of Sweden partner on SMRs</t>
+          <t>Statement of the G7 Non-Proliferation Directors Group</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Ottawa</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
@@ -6587,7 +6085,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6597,43 +6095,38 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>https://www.world-nuclear-news.org/articles/blykalla-and-research-institutes-of-sweden-partnership</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>(59.3251172, 18.0710935)</t>
+          <t>https://www.canada.ca/en/global-affairs/news/2025/08/statement-of-the-g7-non-proliferation-directors-group.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Incident</t>
+          <t>Report</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Thai army confirms white phosphorus use in border fighting</t>
+          <t>Update 310 – IAEA Director General Statement on Situation in Ukraine</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Zaporizhzhia</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
-        <v>45889</v>
+        <v>45891</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -6643,53 +6136,48 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>https://www.intellinews.com/thai-army-confirms-white-phosphorus-use-in-border-fighting-396974/</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>(13.7524938, 100.4935089)</t>
+          <t>https://www.iaea.org/newscenter/pressreleases/update-310-iaea-director-general-statement-on-situation-in-ukraine</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Report</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Respiratory Virus Surveillance in the WHO African Region Epidemiological Week 34, August 19 to 25 2024</t>
+          <t>Inside the hot zone: OPCW trains experts with live chemical agents</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Geneve</t>
+          <t>Bratislava</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>45889</v>
+        <v>45891</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -6699,7 +6187,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6709,43 +6197,38 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>https://www.afro.who.int/publications/respiratory-virus-surveillance-who-african-region-epidemiological-week-34-august-19-25</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>(46.2017559, 6.1466014)</t>
+          <t>https://www.opcw.org/media-centre/news/2025/08/inside-hot-zone-opcw-trains-experts-live-chemical-agents</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Study</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Artificial intelligence tool for cassava viral diseases diagnosis using participatory surveillance in Burkina FasoProvisionally accepted</t>
+          <t>Ukraine drone hits Russian nuclear plant, sparks huge fire at Novatek's Ust-Luga terminal</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ouagadougou</t>
+          <t>Kursk</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>45889</v>
+        <v>45893</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -6755,22 +6238,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>https://www.frontiersin.org/journals/sustainable-food-systems/articles/10.3389/fsufs.2025.1597039/abstract</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>(12.3681873, -1.5270944)</t>
+          <t>https://www.reuters.com/world/europe/ukraine-drone-hits-russian-nuclear-plant-sparks-huge-fire-novateks-ust-luga-2025-08-24/</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6260,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Nuclear</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CDC Outbreak Communications Toolkit</t>
+          <t>US warns Iran of joint sanctions with Europe ahead of nuclear talks</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6797,11 +6275,11 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Washington D.C.</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>45888</v>
+        <v>45892</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -6811,7 +6289,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -6821,12 +6299,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/west-nile-virus/php/outbreak-communication/index.html</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://shafaq.com/en/Middle-East/US-warns-Iran-of-joint-sanctions-with-Europe-ahead-of-nuclear-talks</t>
         </is>
       </c>
     </row>
@@ -6843,21 +6316,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Machine learning model maps West Nile virus risk in Northeast US</t>
+          <t>UAE sends 30 tonnes of medical aid to Chad to combat cholera outbreak</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Abu Dhabi</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>45888</v>
+        <v>45892</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -6877,12 +6350,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>https://medicalxpress.com/news/2025-08-machine-west-nile-virus-northeast.html</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://www.thenationalnews.com/news/uae/2025/08/23/uae-sends-30-tonnes-of-medical-aid-to-chad-to-combat-cholera-outbreak/</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6362,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Biological</t>
+          <t>Chemical, Biological, Radiological, Nuclear</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Machine learning model maps West Nile virus risk in Northeast US</t>
+          <t>Anthropic Unveils AI Safety Filters to Nix CBRN Weapon Data</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -6909,11 +6377,11 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>45888</v>
+        <v>45892</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -6923,7 +6391,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Weapon</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -6933,29 +6401,24 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>https://medicalxpress.com/news/2025-08-machine-west-nile-virus-northeast.html</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
+          <t>https://opentools.ai/news/anthropic-unveils-ai-safety-filters-to-nix-cbrn-weapon-data</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Exercise</t>
+          <t>Incident</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Radiological</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>U.S. Army taps INL’s nuclear expertise, capabilities to strengthen radiological response and readiness</t>
+          <t>Mandatory evacuation remains as fire from Louisiana plant explosion continues to burn</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6965,11 +6428,11 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Louisiana</t>
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>45889</v>
+        <v>45893</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -6979,7 +6442,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -6989,12 +6452,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>https://inl.gov/feature-story/u-s-army-taps-inls-nuclear-expertise-capabilities-to-strengthen-radiological-response-and-readiness/</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>(43.4887907, -112.03628)</t>
+          <t>https://abcnews.go.com/US/explosion-louisiana-business-evacuation/story?id=124900678</t>
         </is>
       </c>
     </row>
@@ -7006,26 +6464,26 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Nuclear</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Enhancing Radiological Data Exchange and Strengthening Cooperation in Nuclear Safety between the EU and the Western Balkans</t>
+          <t>Ukrainian man arrested in Italy over Nord Stream pipeline explosion</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brussels</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>45889</v>
+        <v>45891</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -7035,7 +6493,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Environmental</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7045,1228 +6503,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>https://enlargement.ec.europa.eu/news/enhancing-radiological-data-exchange-and-strengthening-cooperation-nuclear-safety-between-eu-and-2025-08-20_en</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>(50.8465573, 4.351697)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Enhancing Radiological Data Exchange and Strengthening Cooperation in Nuclear Safety between the EU and the Western Balkans</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Brussels</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>https://enlargement.ec.europa.eu/news/enhancing-radiological-data-exchange-and-strengthening-cooperation-nuclear-safety-between-eu-and-2025-08-20_en</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>(50.8465573, 4.351697)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Japan and South Korea Reportedly Consider Nuclear Weapons Amid Regional Threats</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Tokyo</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>https://united24media.com/latest-news/japan-and-south-korea-reportedly-consider-nuclear-weapons-amid-regional-threats-10931</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>(34.7811578, 135.4699059)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Japan and South Korea Reportedly Consider Nuclear Weapons Amid Regional Threats</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Seoul</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>https://united24media.com/latest-news/japan-and-south-korea-reportedly-consider-nuclear-weapons-amid-regional-threats-10931</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>(37.5666791, 126.9782914)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Walmart Recalls Frozen Shrimp After Radioactive Contamination Warning</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>https://www.nytimes.com/2025/08/20/business/radioactive-shrimp-walmart-recall.html</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>(39.5162401, -76.9382069)</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Exercise</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Jordan Enhances Nuclear Emergency Readiness Through "Dragon Eye" Exercise</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Petra</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>https://www.petra.gov.jo/Include/InnerPage.jsp?ID=74765&amp;lang=en&amp;name=en_news</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>(-26.3458594, -48.8318147)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Smoke prompts automatic shutdown at Busan's Shin-Kori Unit 1 nuclear plant</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>Busan</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>45890</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>https://biz.chosun.com/en/en-industry/2025/08/21/O4HNPSXHBBHIDOLES2AGR2CXTM/</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>(35.1799528, 129.0752365)</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Italy Boosts Security at Aviano US Nuclear Base Amid Russian Sabotage Fears</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aviano </t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>45888</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>https://thedefensepost.com/2025/08/19/italy-us-nuclear-russia/</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>(46.0644488, 12.5905671)</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Statement of the G7 Non-Proliferation Directors Group</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Ottawa</t>
-        </is>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/en/global-affairs/news/2025/08/statement-of-the-g7-non-proliferation-directors-group.html</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>(45.4208777, -75.6901106)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Statement of the G7 Non-Proliferation Directors Group</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Ottawa</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/en/global-affairs/news/2025/08/statement-of-the-g7-non-proliferation-directors-group.html</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>(45.4208777, -75.6901106)</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Statement of the G7 Non-Proliferation Directors Group</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Ottawa</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/en/global-affairs/news/2025/08/statement-of-the-g7-non-proliferation-directors-group.html</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>(45.4208777, -75.6901106)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Statement of the G7 Non-Proliferation Directors Group</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Ottawa</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>45889</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/en/global-affairs/news/2025/08/statement-of-the-g7-non-proliferation-directors-group.html</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>(45.4208777, -75.6901106)</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Report</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Update 310 – IAEA Director General Statement on Situation in Ukraine</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Ukraine</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Zaporizhzhia</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>45891</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>https://www.iaea.org/newscenter/pressreleases/update-310-iaea-director-general-statement-on-situation-in-ukraine</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>(47.8507859, 35.1182867)</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Inside the hot zone: OPCW trains experts with live chemical agents</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Bratislava</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>45891</v>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>https://www.opcw.org/media-centre/news/2025/08/inside-hot-zone-opcw-trains-experts-live-chemical-agents</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>(48.1516988, 17.1093063)</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Ukraine drone hits Russian nuclear plant, sparks huge fire at Novatek's Ust-Luga terminal</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Russia</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Kursk</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>45893</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>https://www.reuters.com/world/europe/ukraine-drone-hits-russian-nuclear-plant-sparks-huge-fire-novateks-ust-luga-2025-08-24/</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>(51.7270356, 36.192248)</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>US warns Iran of joint sanctions with Europe ahead of nuclear talks</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Washington D.C.</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>45892</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>https://shafaq.com/en/Middle-East/US-warns-Iran-of-joint-sanctions-with-Europe-ahead-of-nuclear-talks</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>(38.8950368, -77.0365427)</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>UAE sends 30 tonnes of medical aid to Chad to combat cholera outbreak</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Abu Dhabi</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>45892</v>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>https://www.thenationalnews.com/news/uae/2025/08/23/uae-sends-30-tonnes-of-medical-aid-to-chad-to-combat-cholera-outbreak/</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>(24.4538352, 54.3774014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Anthropic Unveils AI Safety Filters to Nix CBRN Weapon Data</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>45892</v>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>https://opentools.ai/news/anthropic-unveils-ai-safety-filters-to-nix-cbrn-weapon-data</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Biological</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Anthropic Unveils AI Safety Filters to Nix CBRN Weapon Data</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>45892</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>https://opentools.ai/news/anthropic-unveils-ai-safety-filters-to-nix-cbrn-weapon-data</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Radiological</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Anthropic Unveils AI Safety Filters to Nix CBRN Weapon Data</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>45892</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>https://opentools.ai/news/anthropic-unveils-ai-safety-filters-to-nix-cbrn-weapon-data</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Nuclear</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Anthropic Unveils AI Safety Filters to Nix CBRN Weapon Data</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>45892</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>https://opentools.ai/news/anthropic-unveils-ai-safety-filters-to-nix-cbrn-weapon-data</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Incident</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Mandatory evacuation remains as fire from Louisiana plant explosion continues to burn</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Louisiana</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>45893</v>
-      </c>
-      <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Environmental</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>https://abcnews.go.com/US/explosion-louisiana-business-evacuation/story?id=124900678</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>(30.8703881, -92.007126)</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Ukrainian man arrested in Italy over Nord Stream pipeline explosion</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Rimini</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>45891</v>
-      </c>
-      <c r="G141" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Infrastructure</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
           <t>https://www.upstreamonline.com/energy-security/ukrainian-man-arrested-in-italy-over-nord-stream-pipeline-explosion/2-1-1861351</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>(43.9465433, 12.630749)</t>
         </is>
       </c>
     </row>
